--- a/data/LoginTestData.xlsx
+++ b/data/LoginTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ppham\Documents\Do an\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E385F8C1-28EB-4E72-BBE1-004A8A24C1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0610BC-F7DC-45E4-8509-E755AB0B0678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2F9B1718-7680-4F4C-BE2C-0BB9EDB9855F}"/>
+    <workbookView xWindow="3516" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{2F9B1718-7680-4F4C-BE2C-0BB9EDB9855F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -484,131 +484,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25CF42E1-7F4A-46BF-8AF4-3C5122D6BD8C}">
-  <dimension ref="B2:F8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="20.21875" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" customWidth="1"/>
-    <col min="5" max="5" width="27.21875" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>7</v>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{2D3F256F-14D8-4DF7-AF6B-F1DA0C48945C}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{91FA058F-9DFE-4B67-80CE-176594E0C2D4}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{E85B9371-1C28-46A7-9768-CF1C739DB9EF}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{2D3F256F-14D8-4DF7-AF6B-F1DA0C48945C}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{91FA058F-9DFE-4B67-80CE-176594E0C2D4}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{E85B9371-1C28-46A7-9768-CF1C739DB9EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
